--- a/tests/reference_data/test_scenario_fms_constrained_abs.xlsx
+++ b/tests/reference_data/test_scenario_fms_constrained_abs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\PythonProjects\aiphoria\tests\reference_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF368309-5F85-488D-AE68-43E0B5C4A8AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A80A6C75-2EF6-4A73-A833-54BE95DF8E65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6195" yWindow="3285" windowWidth="21600" windowHeight="11295" activeTab="5" xr2:uid="{1000A452-A98F-45C1-B843-91F7F67E097C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1000A452-A98F-45C1-B843-91F7F67E097C}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="11" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="216">
   <si>
     <t>Years</t>
   </si>
@@ -735,6 +735,12 @@
   </si>
   <si>
     <t>Target value - target opposite flows</t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
+    <t>Scenario file format version</t>
   </si>
 </sst>
 </file>
@@ -1387,7 +1393,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89FFA668-DA1A-459B-BD42-D0D7F7709F0D}">
-  <dimension ref="A2:E41"/>
+  <dimension ref="A2:E42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
@@ -1431,173 +1437,170 @@
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C7" s="23" t="s">
-        <v>1</v>
+        <v>214</v>
+      </c>
+      <c r="C7" s="22">
+        <v>2</v>
       </c>
       <c r="D7" s="23" t="s">
         <v>71</v>
       </c>
       <c r="E7" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>119</v>
-      </c>
-      <c r="C8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D8" t="s">
-        <v>104</v>
+        <v>43</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="23" t="s">
+        <v>71</v>
       </c>
       <c r="E8" t="s">
-        <v>121</v>
+        <v>198</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>44</v>
-      </c>
-      <c r="C9" s="22">
-        <v>2</v>
-      </c>
-      <c r="D9" s="22" t="s">
-        <v>69</v>
+        <v>119</v>
+      </c>
+      <c r="C9" t="s">
+        <v>150</v>
+      </c>
+      <c r="D9" t="s">
+        <v>104</v>
       </c>
       <c r="E9" t="s">
-        <v>47</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C10" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="22">
         <v>2</v>
       </c>
-      <c r="D10" s="23" t="s">
-        <v>70</v>
+      <c r="D10" s="22" t="s">
+        <v>69</v>
       </c>
       <c r="E10" t="s">
-        <v>197</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>120</v>
-      </c>
-      <c r="C11" t="s">
-        <v>150</v>
-      </c>
-      <c r="D11" t="s">
-        <v>104</v>
+        <v>45</v>
+      </c>
+      <c r="C11" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="23" t="s">
+        <v>70</v>
       </c>
       <c r="E11" t="s">
-        <v>122</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>46</v>
-      </c>
-      <c r="C12" s="22">
-        <v>2</v>
-      </c>
-      <c r="D12" s="22" t="s">
-        <v>69</v>
+        <v>120</v>
+      </c>
+      <c r="C12" t="s">
+        <v>150</v>
+      </c>
+      <c r="D12" t="s">
+        <v>104</v>
       </c>
       <c r="E12" t="s">
-        <v>47</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C13" s="22">
-        <v>2000</v>
+        <v>2</v>
       </c>
       <c r="D13" s="22" t="s">
         <v>69</v>
       </c>
       <c r="E13" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C14" s="22">
-        <v>2010</v>
+        <v>2000</v>
       </c>
       <c r="D14" s="22" t="s">
         <v>69</v>
       </c>
       <c r="E14" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>51</v>
-      </c>
-      <c r="C15" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D15" t="s">
-        <v>68</v>
+        <v>50</v>
+      </c>
+      <c r="C15" s="22">
+        <v>2010</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>69</v>
       </c>
       <c r="E15" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C16" s="24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16" t="s">
         <v>68</v>
       </c>
       <c r="E16" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D17" t="s">
+        <v>68</v>
+      </c>
+      <c r="E17" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
         <v>62</v>
       </c>
-      <c r="C17" s="14">
+      <c r="C18" s="14">
         <v>0.1</v>
       </c>
-      <c r="D17" s="22" t="s">
+      <c r="D18" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E18" t="s">
         <v>63</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>166</v>
-      </c>
-      <c r="B18" t="s">
-        <v>142</v>
-      </c>
-      <c r="C18" t="s">
-        <v>149</v>
-      </c>
-      <c r="D18" t="s">
-        <v>70</v>
-      </c>
-      <c r="E18" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -1605,16 +1608,16 @@
         <v>166</v>
       </c>
       <c r="B19" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C19" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D19" t="s">
         <v>70</v>
       </c>
       <c r="E19" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -1622,16 +1625,16 @@
         <v>166</v>
       </c>
       <c r="B20" t="s">
-        <v>56</v>
-      </c>
-      <c r="C20" s="20">
-        <v>-3.6666666666666701</v>
-      </c>
-      <c r="D20" s="20" t="s">
-        <v>72</v>
+        <v>143</v>
+      </c>
+      <c r="C20" t="s">
+        <v>146</v>
+      </c>
+      <c r="D20" t="s">
+        <v>70</v>
       </c>
       <c r="E20" t="s">
-        <v>57</v>
+        <v>144</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -1639,16 +1642,16 @@
         <v>166</v>
       </c>
       <c r="B21" t="s">
-        <v>66</v>
-      </c>
-      <c r="C21" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="D21" t="s">
-        <v>68</v>
+        <v>56</v>
+      </c>
+      <c r="C21" s="20">
+        <v>-3.6666666666666701</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>72</v>
       </c>
       <c r="E21" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -1656,7 +1659,7 @@
         <v>166</v>
       </c>
       <c r="B22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C22" s="24" t="b">
         <v>1</v>
@@ -1673,16 +1676,16 @@
         <v>166</v>
       </c>
       <c r="B23" t="s">
-        <v>73</v>
-      </c>
-      <c r="C23" t="s">
-        <v>76</v>
+        <v>65</v>
+      </c>
+      <c r="C23" s="24" t="b">
+        <v>1</v>
       </c>
       <c r="D23" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E23" t="s">
-        <v>94</v>
+        <v>67</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -1690,16 +1693,16 @@
         <v>166</v>
       </c>
       <c r="B24" t="s">
-        <v>153</v>
-      </c>
-      <c r="C24" s="24" t="b">
-        <v>1</v>
+        <v>73</v>
+      </c>
+      <c r="C24" t="s">
+        <v>76</v>
       </c>
       <c r="D24" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E24" t="s">
-        <v>154</v>
+        <v>94</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -1707,16 +1710,16 @@
         <v>166</v>
       </c>
       <c r="B25" t="s">
-        <v>161</v>
-      </c>
-      <c r="C25" t="s">
-        <v>163</v>
+        <v>153</v>
+      </c>
+      <c r="C25" s="24" t="b">
+        <v>1</v>
       </c>
       <c r="D25" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E25" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -1724,16 +1727,16 @@
         <v>166</v>
       </c>
       <c r="B26" t="s">
-        <v>79</v>
+        <v>161</v>
       </c>
       <c r="C26" t="s">
-        <v>80</v>
+        <v>163</v>
       </c>
       <c r="D26" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E26" t="s">
-        <v>196</v>
+        <v>165</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -1741,16 +1744,16 @@
         <v>166</v>
       </c>
       <c r="B27" t="s">
-        <v>130</v>
+        <v>79</v>
       </c>
       <c r="C27" t="s">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="D27" t="s">
-        <v>104</v>
+        <v>70</v>
       </c>
       <c r="E27" t="s">
-        <v>132</v>
+        <v>196</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -1758,16 +1761,16 @@
         <v>166</v>
       </c>
       <c r="B28" t="s">
-        <v>81</v>
-      </c>
-      <c r="C28" s="24" t="b">
-        <v>1</v>
+        <v>130</v>
+      </c>
+      <c r="C28" t="s">
+        <v>150</v>
       </c>
       <c r="D28" t="s">
-        <v>68</v>
+        <v>104</v>
       </c>
       <c r="E28" t="s">
-        <v>82</v>
+        <v>132</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -1775,7 +1778,7 @@
         <v>166</v>
       </c>
       <c r="B29" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C29" s="24" t="b">
         <v>1</v>
@@ -1784,7 +1787,7 @@
         <v>68</v>
       </c>
       <c r="E29" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -1792,13 +1795,16 @@
         <v>166</v>
       </c>
       <c r="B30" t="s">
-        <v>102</v>
+        <v>83</v>
+      </c>
+      <c r="C30" s="24" t="b">
+        <v>1</v>
       </c>
       <c r="D30" t="s">
-        <v>104</v>
+        <v>68</v>
       </c>
       <c r="E30" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -1806,16 +1812,13 @@
         <v>166</v>
       </c>
       <c r="B31" t="s">
-        <v>112</v>
-      </c>
-      <c r="C31" s="22" t="s">
-        <v>113</v>
-      </c>
-      <c r="D31" s="22" t="s">
-        <v>70</v>
+        <v>102</v>
+      </c>
+      <c r="D31" t="s">
+        <v>104</v>
       </c>
       <c r="E31" t="s">
-        <v>195</v>
+        <v>103</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -1823,41 +1826,44 @@
         <v>166</v>
       </c>
       <c r="B32" t="s">
-        <v>131</v>
-      </c>
-      <c r="D32" t="s">
-        <v>104</v>
+        <v>112</v>
+      </c>
+      <c r="C32" s="22" t="s">
+        <v>113</v>
+      </c>
+      <c r="D32" s="22" t="s">
+        <v>70</v>
       </c>
       <c r="E32" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>166</v>
       </c>
       <c r="B33" t="s">
-        <v>156</v>
+        <v>131</v>
       </c>
       <c r="D33" t="s">
         <v>104</v>
       </c>
       <c r="E33" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>166</v>
       </c>
       <c r="B34" t="s">
-        <v>199</v>
+        <v>156</v>
       </c>
       <c r="D34" t="s">
         <v>104</v>
       </c>
       <c r="E34" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -1865,16 +1871,13 @@
         <v>166</v>
       </c>
       <c r="B35" t="s">
-        <v>167</v>
-      </c>
-      <c r="C35" t="s">
-        <v>168</v>
+        <v>199</v>
       </c>
       <c r="D35" t="s">
-        <v>70</v>
+        <v>104</v>
       </c>
       <c r="E35" t="s">
-        <v>194</v>
+        <v>157</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -1882,16 +1885,16 @@
         <v>166</v>
       </c>
       <c r="B36" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C36" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D36" t="s">
         <v>70</v>
       </c>
       <c r="E36" t="s">
-        <v>172</v>
+        <v>194</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -1899,16 +1902,16 @@
         <v>166</v>
       </c>
       <c r="B37" t="s">
-        <v>173</v>
-      </c>
-      <c r="C37" s="24" t="b">
-        <v>1</v>
+        <v>170</v>
+      </c>
+      <c r="C37" t="s">
+        <v>171</v>
       </c>
       <c r="D37" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E37" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -1916,7 +1919,7 @@
         <v>166</v>
       </c>
       <c r="B38" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="C38" s="24" t="b">
         <v>1</v>
@@ -1925,7 +1928,7 @@
         <v>68</v>
       </c>
       <c r="E38" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -1933,16 +1936,16 @@
         <v>166</v>
       </c>
       <c r="B39" t="s">
-        <v>187</v>
-      </c>
-      <c r="C39" t="s">
-        <v>188</v>
+        <v>185</v>
+      </c>
+      <c r="C39" s="24" t="b">
+        <v>1</v>
       </c>
       <c r="D39" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E39" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -1950,16 +1953,16 @@
         <v>166</v>
       </c>
       <c r="B40" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C40" t="s">
-        <v>150</v>
+        <v>188</v>
       </c>
       <c r="D40" t="s">
-        <v>104</v>
+        <v>70</v>
       </c>
       <c r="E40" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -1967,21 +1970,38 @@
         <v>166</v>
       </c>
       <c r="B41" t="s">
+        <v>189</v>
+      </c>
+      <c r="C41" t="s">
+        <v>150</v>
+      </c>
+      <c r="D41" t="s">
+        <v>104</v>
+      </c>
+      <c r="E41" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>166</v>
+      </c>
+      <c r="B42" t="s">
         <v>191</v>
       </c>
-      <c r="C41">
+      <c r="C42">
         <v>2</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D42" t="s">
         <v>69</v>
       </c>
-      <c r="E41" t="s">
+      <c r="E42" t="s">
         <v>192</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="B6:E6" xr:uid="{89FFA668-DA1A-459B-BD42-D0D7F7709F0D}"/>
-  <conditionalFormatting sqref="C15:C16">
+  <conditionalFormatting sqref="C16:C17">
     <cfRule type="cellIs" dxfId="11" priority="11" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
@@ -1989,7 +2009,7 @@
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C21:C22">
+  <conditionalFormatting sqref="C22:C23">
     <cfRule type="cellIs" dxfId="9" priority="9" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
@@ -1997,7 +2017,7 @@
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C24">
+  <conditionalFormatting sqref="C25">
     <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
@@ -2005,7 +2025,7 @@
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C28:C29">
+  <conditionalFormatting sqref="C29:C30">
     <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
@@ -2013,7 +2033,7 @@
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C37:C38">
+  <conditionalFormatting sqref="C38:C39">
     <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
@@ -2022,7 +2042,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C15:C16 C21:C22 C28:C29 C24 C37:C38" xr:uid="{79A7E31C-3284-4405-9B5F-03E099B07563}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C16:C17 C22:C23 C29:C30 C25 C38:C39" xr:uid="{79A7E31C-3284-4405-9B5F-03E099B07563}">
       <formula1>Boolean</formula1>
     </dataValidation>
   </dataValidations>
@@ -2035,13 +2055,13 @@
           <x14:formula1>
             <xm:f>'Data validation parameters'!$D$6:$D$9</xm:f>
           </x14:formula1>
-          <xm:sqref>C23</xm:sqref>
+          <xm:sqref>C24</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7A04E2A2-4928-4E28-9F6D-7D556381B8E8}">
           <x14:formula1>
             <xm:f>'Data validation parameters'!$G$6:$G$7</xm:f>
           </x14:formula1>
-          <xm:sqref>C25</xm:sqref>
+          <xm:sqref>C26</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3649,27 +3669,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7536dd80-7d39-48e8-9ae3-b4166f580a2d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="145cc194-9bea-4db6-b116-a042a4529fcd" xsi:nil="true"/>
-    <Comment xmlns="7536dd80-7d39-48e8-9ae3-b4166f580a2d" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Asiakirja" ma:contentTypeID="0x010100806C55B750152A459818B636E97A41C3" ma:contentTypeVersion="19" ma:contentTypeDescription="Luo uusi asiakirja." ma:contentTypeScope="" ma:versionID="74fd9cb75cef04cf26a1ff9ddef01b4b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7536dd80-7d39-48e8-9ae3-b4166f580a2d" xmlns:ns3="145cc194-9bea-4db6-b116-a042a4529fcd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="afbcbfdd38894bc2ff0644b00c8ec680" ns2:_="" ns3:_="">
     <xsd:import namespace="7536dd80-7d39-48e8-9ae3-b4166f580a2d"/>
@@ -3932,32 +3931,28 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{557FAA9C-B184-448F-B58D-00E4D46BDD72}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="7536dd80-7d39-48e8-9ae3-b4166f580a2d"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="145cc194-9bea-4db6-b116-a042a4529fcd"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8AB3C6F0-DB35-46F0-8FEB-B5E57B48A727}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7536dd80-7d39-48e8-9ae3-b4166f580a2d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="145cc194-9bea-4db6-b116-a042a4529fcd" xsi:nil="true"/>
+    <Comment xmlns="7536dd80-7d39-48e8-9ae3-b4166f580a2d" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D60021C7-CA75-4673-96EA-55284BF81134}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3974,4 +3969,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8AB3C6F0-DB35-46F0-8FEB-B5E57B48A727}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{557FAA9C-B184-448F-B58D-00E4D46BDD72}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="7536dd80-7d39-48e8-9ae3-b4166f580a2d"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="145cc194-9bea-4db6-b116-a042a4529fcd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/tests/reference_data/test_scenario_fms_constrained_abs.xlsx
+++ b/tests/reference_data/test_scenario_fms_constrained_abs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\PythonProjects\aiphoria\tests\reference_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A80A6C75-2EF6-4A73-A833-54BE95DF8E65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44CCE14C-B143-44A1-A27D-289D65FEB711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1000A452-A98F-45C1-B843-91F7F67E097C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{1000A452-A98F-45C1-B843-91F7F67E097C}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="11" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <sheet name="Data validation parameters" sheetId="9" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Flows!$A$3:$P$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Flows!$A$3:$H$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Processes!$D$3:$R$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Settings!$B$6:$E$6</definedName>
     <definedName name="Boolean">'Data validation parameters'!$C$6:$C$7</definedName>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="210">
   <si>
     <t>Years</t>
   </si>
@@ -497,30 +497,12 @@
     <t>Ignore Excel columns defined in the list when reading data from Colors sheet. Each column name must be separated by comma (',')</t>
   </si>
   <si>
-    <t>Source process</t>
-  </si>
-  <si>
-    <t>Source process location</t>
-  </si>
-  <si>
-    <t>Target process</t>
-  </si>
-  <si>
-    <t>Target process location</t>
-  </si>
-  <si>
     <t>Source ID</t>
   </si>
   <si>
     <t>Target ID</t>
   </si>
   <si>
-    <t>Data source</t>
-  </si>
-  <si>
-    <t>Data source comment</t>
-  </si>
-  <si>
     <t>baseline_value_name</t>
   </si>
   <si>
@@ -698,9 +680,6 @@
     <t>Middle</t>
   </si>
   <si>
-    <t>Test values</t>
-  </si>
-  <si>
     <t>Middle:FI</t>
   </si>
   <si>
@@ -741,6 +720,9 @@
   </si>
   <si>
     <t>Scenario file format version</t>
+  </si>
+  <si>
+    <t>Source:FI</t>
   </si>
 </sst>
 </file>
@@ -890,20 +872,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1057,8 +1032,8 @@
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>219909</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>343734</xdr:colOff>
       <xdr:row>22</xdr:row>
       <xdr:rowOff>19412</xdr:rowOff>
     </xdr:to>
@@ -1404,12 +1379,12 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="21" x14ac:dyDescent="0.35">
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="16" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="18" t="s">
         <v>60</v>
       </c>
     </row>
@@ -1417,50 +1392,50 @@
       <c r="B4" t="s">
         <v>59</v>
       </c>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="6" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>214</v>
-      </c>
-      <c r="C7" s="22">
+        <v>207</v>
+      </c>
+      <c r="C7" s="19">
         <v>2</v>
       </c>
-      <c r="D7" s="23" t="s">
+      <c r="D7" s="20" t="s">
         <v>71</v>
       </c>
       <c r="E7" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>43</v>
       </c>
-      <c r="C8" s="23" t="s">
+      <c r="C8" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="23" t="s">
+      <c r="D8" s="20" t="s">
         <v>71</v>
       </c>
       <c r="E8" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.25">
@@ -1468,7 +1443,7 @@
         <v>119</v>
       </c>
       <c r="C9" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D9" t="s">
         <v>104</v>
@@ -1481,10 +1456,10 @@
       <c r="B10" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="22">
+      <c r="C10" s="19">
         <v>2</v>
       </c>
-      <c r="D10" s="22" t="s">
+      <c r="D10" s="19" t="s">
         <v>69</v>
       </c>
       <c r="E10" t="s">
@@ -1495,14 +1470,14 @@
       <c r="B11" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="23" t="s">
+      <c r="C11" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="D11" s="23" t="s">
+      <c r="D11" s="20" t="s">
         <v>70</v>
       </c>
       <c r="E11" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.25">
@@ -1510,7 +1485,7 @@
         <v>120</v>
       </c>
       <c r="C12" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D12" t="s">
         <v>104</v>
@@ -1523,10 +1498,10 @@
       <c r="B13" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="22">
+      <c r="C13" s="19">
         <v>2</v>
       </c>
-      <c r="D13" s="22" t="s">
+      <c r="D13" s="19" t="s">
         <v>69</v>
       </c>
       <c r="E13" t="s">
@@ -1537,10 +1512,10 @@
       <c r="B14" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="22">
+      <c r="C14" s="19">
         <v>2000</v>
       </c>
-      <c r="D14" s="22" t="s">
+      <c r="D14" s="19" t="s">
         <v>69</v>
       </c>
       <c r="E14" t="s">
@@ -1551,10 +1526,10 @@
       <c r="B15" t="s">
         <v>50</v>
       </c>
-      <c r="C15" s="22">
+      <c r="C15" s="19">
         <v>2010</v>
       </c>
-      <c r="D15" s="22" t="s">
+      <c r="D15" s="19" t="s">
         <v>69</v>
       </c>
       <c r="E15" t="s">
@@ -1565,7 +1540,7 @@
       <c r="B16" t="s">
         <v>51</v>
       </c>
-      <c r="C16" s="24" t="b">
+      <c r="C16" s="21" t="b">
         <v>0</v>
       </c>
       <c r="D16" t="s">
@@ -1579,7 +1554,7 @@
       <c r="B17" t="s">
         <v>54</v>
       </c>
-      <c r="C17" s="24" t="b">
+      <c r="C17" s="21" t="b">
         <v>1</v>
       </c>
       <c r="D17" t="s">
@@ -1593,10 +1568,10 @@
       <c r="B18" t="s">
         <v>62</v>
       </c>
-      <c r="C18" s="14">
+      <c r="C18" s="11">
         <v>0.1</v>
       </c>
-      <c r="D18" s="22" t="s">
+      <c r="D18" s="19" t="s">
         <v>72</v>
       </c>
       <c r="E18" t="s">
@@ -1605,49 +1580,49 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="B19" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C19" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="D19" t="s">
         <v>70</v>
       </c>
       <c r="E19" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="B20" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="C20" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="D20" t="s">
         <v>70</v>
       </c>
       <c r="E20" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="B21" t="s">
         <v>56</v>
       </c>
-      <c r="C21" s="20">
+      <c r="C21" s="17">
         <v>-3.6666666666666701</v>
       </c>
-      <c r="D21" s="20" t="s">
+      <c r="D21" s="17" t="s">
         <v>72</v>
       </c>
       <c r="E21" t="s">
@@ -1656,12 +1631,12 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="B22" t="s">
         <v>66</v>
       </c>
-      <c r="C22" s="24" t="b">
+      <c r="C22" s="21" t="b">
         <v>1</v>
       </c>
       <c r="D22" t="s">
@@ -1673,12 +1648,12 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="B23" t="s">
         <v>65</v>
       </c>
-      <c r="C23" s="24" t="b">
+      <c r="C23" s="21" t="b">
         <v>1</v>
       </c>
       <c r="D23" t="s">
@@ -1690,7 +1665,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="B24" t="s">
         <v>73</v>
@@ -1707,41 +1682,41 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="B25" t="s">
-        <v>153</v>
-      </c>
-      <c r="C25" s="24" t="b">
+        <v>147</v>
+      </c>
+      <c r="C25" s="21" t="b">
         <v>1</v>
       </c>
       <c r="D25" t="s">
         <v>68</v>
       </c>
       <c r="E25" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="B26" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="C26" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="D26" t="s">
         <v>71</v>
       </c>
       <c r="E26" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="B27" t="s">
         <v>79</v>
@@ -1753,18 +1728,18 @@
         <v>70</v>
       </c>
       <c r="E27" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="B28" t="s">
         <v>130</v>
       </c>
       <c r="C28" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D28" t="s">
         <v>104</v>
@@ -1775,12 +1750,12 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="B29" t="s">
         <v>81</v>
       </c>
-      <c r="C29" s="24" t="b">
+      <c r="C29" s="21" t="b">
         <v>1</v>
       </c>
       <c r="D29" t="s">
@@ -1792,12 +1767,12 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="B30" t="s">
         <v>83</v>
       </c>
-      <c r="C30" s="24" t="b">
+      <c r="C30" s="21" t="b">
         <v>1</v>
       </c>
       <c r="D30" t="s">
@@ -1809,7 +1784,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="B31" t="s">
         <v>102</v>
@@ -1823,24 +1798,24 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="B32" t="s">
         <v>112</v>
       </c>
-      <c r="C32" s="22" t="s">
+      <c r="C32" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="D32" s="22" t="s">
+      <c r="D32" s="19" t="s">
         <v>70</v>
       </c>
       <c r="E32" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="B33" t="s">
         <v>131</v>
@@ -1854,140 +1829,140 @@
     </row>
     <row r="34" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="B34" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="D34" t="s">
         <v>104</v>
       </c>
       <c r="E34" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="B35" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="D35" t="s">
         <v>104</v>
       </c>
       <c r="E35" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="B36" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="C36" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="D36" t="s">
         <v>70</v>
       </c>
       <c r="E36" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="B37" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C37" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="D37" t="s">
         <v>70</v>
       </c>
       <c r="E37" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="B38" t="s">
-        <v>173</v>
-      </c>
-      <c r="C38" s="24" t="b">
+        <v>167</v>
+      </c>
+      <c r="C38" s="21" t="b">
         <v>1</v>
       </c>
       <c r="D38" t="s">
         <v>68</v>
       </c>
       <c r="E38" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="B39" t="s">
-        <v>185</v>
-      </c>
-      <c r="C39" s="24" t="b">
+        <v>179</v>
+      </c>
+      <c r="C39" s="21" t="b">
         <v>1</v>
       </c>
       <c r="D39" t="s">
         <v>68</v>
       </c>
       <c r="E39" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="B40" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="C40" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="D40" t="s">
         <v>70</v>
       </c>
       <c r="E40" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="B41" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="C41" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D41" t="s">
         <v>104</v>
       </c>
       <c r="E41" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="B42" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="C42">
         <v>2</v>
@@ -1996,7 +1971,7 @@
         <v>69</v>
       </c>
       <c r="E42" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
   </sheetData>
@@ -2156,7 +2131,7 @@
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
-      <c r="I2" s="7"/>
+      <c r="I2" s="5"/>
       <c r="J2" s="2" t="s">
         <v>9</v>
       </c>
@@ -2171,59 +2146,59 @@
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
     </row>
-    <row r="3" spans="1:18" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
-        <v>151</v>
-      </c>
-      <c r="B3" s="16" t="s">
+    <row r="3" spans="1:18" s="14" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="B3" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="16" t="s">
+      <c r="E3" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="F3" s="16" t="s">
+      <c r="F3" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="G3" s="16" t="s">
+      <c r="G3" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="H3" s="16" t="s">
+      <c r="H3" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="I3" s="16" t="s">
+      <c r="I3" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="J3" s="16" t="s">
+      <c r="J3" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="K3" s="16" t="s">
+      <c r="K3" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="L3" s="16" t="s">
+      <c r="L3" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="16" t="s">
+      <c r="M3" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="N3" s="16" t="s">
+      <c r="N3" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="O3" s="16" t="s">
+      <c r="O3" s="13" t="s">
         <v>20</v>
       </c>
       <c r="P3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="Q3" s="16" t="s">
+      <c r="Q3" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="R3" s="16" t="s">
+      <c r="R3" s="13" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2260,7 +2235,7 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="C5" t="s">
         <v>25</v>
@@ -2280,7 +2255,7 @@
       </c>
       <c r="M5" s="4"/>
       <c r="R5" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="15.75" x14ac:dyDescent="0.3">
@@ -2288,7 +2263,7 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="C6" t="s">
         <v>25</v>
@@ -2308,7 +2283,7 @@
       </c>
       <c r="M6" s="4"/>
       <c r="R6" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="15.75" x14ac:dyDescent="0.3">
@@ -2316,7 +2291,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="C7" t="s">
         <v>25</v>
@@ -2336,7 +2311,7 @@
       </c>
       <c r="M7" s="4"/>
       <c r="R7" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2365,28 +2340,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B692AEE8-68EE-4B81-A49D-50BF066DFFE7}">
-  <dimension ref="A1:P82"/>
+  <dimension ref="A1:H82"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.5703125" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" customWidth="1"/>
-    <col min="6" max="6" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24" customWidth="1"/>
-    <col min="9" max="9" width="20.42578125" customWidth="1"/>
-    <col min="10" max="10" width="9.42578125" customWidth="1"/>
-    <col min="11" max="11" width="15.85546875" customWidth="1"/>
-    <col min="12" max="12" width="12.85546875" customWidth="1"/>
-    <col min="13" max="13" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.7109375" customWidth="1"/>
-    <col min="16" max="16" width="42" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="20.42578125" customWidth="1"/>
+    <col min="4" max="4" width="9.42578125" customWidth="1"/>
+    <col min="5" max="5" width="15.85546875" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" customWidth="1"/>
+    <col min="8" max="8" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -2397,625 +2364,422 @@
         <v>5</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
+      <c r="E2" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
+      <c r="G2" s="2" t="s">
+        <v>142</v>
+      </c>
       <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="P2" s="2"/>
-    </row>
-    <row r="3" spans="1:16" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
-        <v>152</v>
-      </c>
-      <c r="B3" s="9" t="s">
+    </row>
+    <row r="3" spans="1:8" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="C3" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="D3" s="9" t="s">
+      <c r="C3" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="E3" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>137</v>
+      <c r="D3" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>141</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="L3" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="M3" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="N3" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="O3" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="P3" s="12" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>32</v>
       </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="str">
-        <f>+_xlfn.XLOOKUP(H4,Processes!$D$4:$D$39,Processes!$E$4:$E$39)</f>
-        <v>Source</v>
-      </c>
-      <c r="D4" t="s">
-        <v>25</v>
+      <c r="B4" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D4">
+        <v>100</v>
       </c>
       <c r="E4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4">
+        <v>2000</v>
+      </c>
+      <c r="H4" s="10"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B5" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="D5">
+        <v>50</v>
+      </c>
+      <c r="E5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5">
+        <v>2000</v>
+      </c>
+      <c r="H5" s="10"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B6" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="F4" t="str">
-        <f>+_xlfn.XLOOKUP(I4,Processes!$D$4:$D$39,Processes!$E$4:$E$39)</f>
-        <v>Source</v>
-      </c>
-      <c r="G4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4" s="3" t="str">
-        <f t="shared" ref="H4:H5" si="0">_xlfn.CONCAT(B4,":",D4)</f>
-        <v>Source:FI</v>
-      </c>
-      <c r="I4" s="3" t="str">
-        <f t="shared" ref="I4:I5" si="1">_xlfn.CONCAT(E4,":",G4)</f>
-        <v>Middle:FI</v>
-      </c>
-      <c r="J4">
-        <v>100</v>
-      </c>
-      <c r="K4" t="s">
+      <c r="D6">
+        <v>50</v>
+      </c>
+      <c r="E6" t="s">
         <v>31</v>
       </c>
-      <c r="L4">
+      <c r="F6">
         <v>2000</v>
       </c>
-      <c r="N4" t="s">
-        <v>201</v>
-      </c>
-      <c r="P4" s="13"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>200</v>
-      </c>
-      <c r="C5" t="str">
-        <f>+_xlfn.XLOOKUP(H5,Processes!$D$4:$D$39,Processes!$E$4:$E$39)</f>
-        <v>Source</v>
-      </c>
-      <c r="D5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" t="s">
-        <v>204</v>
-      </c>
-      <c r="F5" t="str">
-        <f>+_xlfn.XLOOKUP(I5,Processes!$D$4:$D$39,Processes!$E$4:$E$39)</f>
-        <v>Source</v>
-      </c>
-      <c r="G5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>Middle:FI</v>
-      </c>
-      <c r="I5" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>Sink1:FI</v>
-      </c>
-      <c r="J5">
-        <v>50</v>
-      </c>
-      <c r="K5" t="s">
-        <v>31</v>
-      </c>
-      <c r="L5">
-        <v>2000</v>
-      </c>
-      <c r="N5" t="s">
-        <v>201</v>
-      </c>
-      <c r="P5" s="13"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>200</v>
-      </c>
-      <c r="C6" t="str">
-        <f>+_xlfn.XLOOKUP(H6,Processes!$D$4:$D$39,Processes!$E$4:$E$39)</f>
-        <v>Source</v>
-      </c>
-      <c r="D6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" t="s">
-        <v>205</v>
-      </c>
-      <c r="F6" t="str">
-        <f>+_xlfn.XLOOKUP(I6,Processes!$D$4:$D$39,Processes!$E$4:$E$39)</f>
-        <v>Source</v>
-      </c>
-      <c r="G6" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6" s="3" t="str">
-        <f t="shared" ref="H6" si="2">_xlfn.CONCAT(B6,":",D6)</f>
-        <v>Middle:FI</v>
-      </c>
-      <c r="I6" s="3" t="str">
-        <f t="shared" ref="I6" si="3">_xlfn.CONCAT(E6,":",G6)</f>
-        <v>Sink2:FI</v>
-      </c>
-      <c r="J6">
-        <v>50</v>
-      </c>
-      <c r="K6" t="s">
-        <v>31</v>
-      </c>
-      <c r="L6">
-        <v>2000</v>
-      </c>
-      <c r="N6" t="s">
-        <v>201</v>
-      </c>
-      <c r="P6" s="13"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="N7"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="N8"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="N9"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="N10"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="N11"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="N12"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="N13"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="N14"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-    </row>
-    <row r="17" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-    </row>
-    <row r="18" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-    </row>
-    <row r="19" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="N19" s="6"/>
-    </row>
-    <row r="20" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="N20" s="6"/>
-    </row>
-    <row r="21" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-    </row>
-    <row r="22" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-    </row>
-    <row r="23" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-    </row>
-    <row r="24" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-    </row>
-    <row r="25" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-    </row>
-    <row r="26" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="E26" s="13"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-    </row>
-    <row r="27" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-    </row>
-    <row r="28" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
-    </row>
-    <row r="29" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
-    </row>
-    <row r="30" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
-      <c r="N30"/>
-    </row>
-    <row r="31" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
-      <c r="N31"/>
-    </row>
-    <row r="32" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
-      <c r="N32"/>
-    </row>
-    <row r="33" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
-      <c r="N33"/>
-    </row>
-    <row r="34" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="H34" s="3"/>
-      <c r="I34" s="3"/>
-      <c r="N34"/>
-    </row>
-    <row r="35" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="H35" s="3"/>
-      <c r="I35" s="3"/>
-      <c r="N35"/>
-    </row>
-    <row r="36" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C36" s="8"/>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
-      <c r="N36"/>
-    </row>
-    <row r="37" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="H37" s="3"/>
-      <c r="I37" s="3"/>
-      <c r="N37"/>
-    </row>
-    <row r="38" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="H38" s="3"/>
-      <c r="I38" s="3"/>
-      <c r="N38"/>
-    </row>
-    <row r="39" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="H39" s="3"/>
-      <c r="I39" s="3"/>
-      <c r="N39"/>
-    </row>
-    <row r="40" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="H40" s="3"/>
-      <c r="I40" s="3"/>
-      <c r="N40"/>
-    </row>
-    <row r="41" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="H41" s="3"/>
-      <c r="I41" s="3"/>
-      <c r="N41"/>
-    </row>
-    <row r="42" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="H42" s="3"/>
-      <c r="I42" s="3"/>
-      <c r="N42"/>
-    </row>
-    <row r="43" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="H43" s="3"/>
-      <c r="I43" s="3"/>
-      <c r="N43"/>
-    </row>
-    <row r="44" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="H44" s="3"/>
-      <c r="I44" s="3"/>
-      <c r="N44"/>
-    </row>
-    <row r="45" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="H45" s="3"/>
-      <c r="I45" s="3"/>
-      <c r="N45"/>
-    </row>
-    <row r="46" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="H46" s="3"/>
-      <c r="I46" s="3"/>
-      <c r="N46"/>
-    </row>
-    <row r="47" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="H47" s="3"/>
-      <c r="I47" s="3"/>
-      <c r="N47"/>
-    </row>
-    <row r="48" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="H48" s="3"/>
-      <c r="I48" s="3"/>
-      <c r="N48"/>
-    </row>
-    <row r="49" spans="8:14" x14ac:dyDescent="0.25">
-      <c r="H49" s="3"/>
-      <c r="I49" s="3"/>
-      <c r="N49"/>
-    </row>
-    <row r="50" spans="8:14" x14ac:dyDescent="0.25">
-      <c r="H50" s="3"/>
-      <c r="I50" s="3"/>
-      <c r="N50"/>
-    </row>
-    <row r="51" spans="8:14" x14ac:dyDescent="0.25">
-      <c r="H51" s="3"/>
-      <c r="I51" s="3"/>
-      <c r="N51"/>
-    </row>
-    <row r="52" spans="8:14" x14ac:dyDescent="0.25">
-      <c r="H52" s="3"/>
-      <c r="I52" s="3"/>
-      <c r="N52"/>
-    </row>
-    <row r="53" spans="8:14" x14ac:dyDescent="0.25">
-      <c r="H53" s="3"/>
-      <c r="I53" s="3"/>
-      <c r="N53"/>
-    </row>
-    <row r="54" spans="8:14" x14ac:dyDescent="0.25">
-      <c r="H54" s="3"/>
-      <c r="I54" s="3"/>
-      <c r="N54"/>
-    </row>
-    <row r="55" spans="8:14" x14ac:dyDescent="0.25">
-      <c r="H55" s="3"/>
-      <c r="I55" s="3"/>
-      <c r="N55"/>
-    </row>
-    <row r="56" spans="8:14" x14ac:dyDescent="0.25">
-      <c r="H56" s="3"/>
-      <c r="I56" s="3"/>
-      <c r="N56"/>
-    </row>
-    <row r="57" spans="8:14" x14ac:dyDescent="0.25">
-      <c r="H57" s="3"/>
-      <c r="I57" s="3"/>
-      <c r="N57"/>
-    </row>
-    <row r="58" spans="8:14" x14ac:dyDescent="0.25">
-      <c r="H58" s="3"/>
-      <c r="I58" s="3"/>
-      <c r="N58"/>
-    </row>
-    <row r="59" spans="8:14" x14ac:dyDescent="0.25">
-      <c r="H59" s="3"/>
-      <c r="I59" s="3"/>
-      <c r="N59"/>
-    </row>
-    <row r="60" spans="8:14" x14ac:dyDescent="0.25">
-      <c r="H60" s="3"/>
-      <c r="I60" s="3"/>
-      <c r="N60"/>
-    </row>
-    <row r="61" spans="8:14" x14ac:dyDescent="0.25">
-      <c r="H61" s="3"/>
-      <c r="I61" s="3"/>
-      <c r="N61"/>
-    </row>
-    <row r="62" spans="8:14" x14ac:dyDescent="0.25">
-      <c r="H62" s="3"/>
-      <c r="I62" s="3"/>
-      <c r="N62"/>
-    </row>
-    <row r="63" spans="8:14" x14ac:dyDescent="0.25">
-      <c r="H63" s="3"/>
-      <c r="I63" s="3"/>
-      <c r="N63"/>
-    </row>
-    <row r="64" spans="8:14" x14ac:dyDescent="0.25">
-      <c r="H64" s="3"/>
-      <c r="I64" s="3"/>
-      <c r="N64"/>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="H65" s="3"/>
-      <c r="I65" s="3"/>
-      <c r="N65"/>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="H66" s="3"/>
-      <c r="I66" s="3"/>
-      <c r="N66"/>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="H67" s="3"/>
-      <c r="I67" s="3"/>
-      <c r="N67"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="H68" s="3"/>
-      <c r="I68" s="3"/>
-      <c r="N68"/>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="H69" s="3"/>
-      <c r="I69" s="3"/>
-      <c r="N69"/>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="H70" s="3"/>
-      <c r="I70" s="3"/>
-      <c r="N70"/>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="H71" s="3"/>
-      <c r="I71" s="3"/>
-      <c r="N71"/>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="H72" s="3"/>
-      <c r="I72" s="3"/>
-      <c r="N72"/>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="H73" s="3"/>
-      <c r="I73" s="3"/>
-      <c r="N73"/>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="H74" s="3"/>
-      <c r="I74" s="3"/>
-      <c r="N74"/>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="H75" s="3"/>
-      <c r="I75" s="3"/>
-      <c r="N75"/>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="H76" s="3"/>
-      <c r="I76" s="3"/>
-      <c r="N76"/>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="N77"/>
-    </row>
-    <row r="78" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="H6" s="10"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+    </row>
+    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+    </row>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+    </row>
+    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+    </row>
+    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+    </row>
+    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+    </row>
+    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+    </row>
+    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+    </row>
+    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+    </row>
+    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+    </row>
+    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+    </row>
+    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+    </row>
+    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+    </row>
+    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+    </row>
+    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+    </row>
+    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+    </row>
+    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+    </row>
+    <row r="46" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
+    </row>
+    <row r="47" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B47" s="3"/>
+      <c r="C47" s="3"/>
+    </row>
+    <row r="48" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B48" s="3"/>
+      <c r="C48" s="3"/>
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B49" s="3"/>
+      <c r="C49" s="3"/>
+    </row>
+    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
+    </row>
+    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B51" s="3"/>
+      <c r="C51" s="3"/>
+    </row>
+    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B52" s="3"/>
+      <c r="C52" s="3"/>
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B53" s="3"/>
+      <c r="C53" s="3"/>
+    </row>
+    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B54" s="3"/>
+      <c r="C54" s="3"/>
+    </row>
+    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B55" s="3"/>
+      <c r="C55" s="3"/>
+    </row>
+    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B56" s="3"/>
+      <c r="C56" s="3"/>
+    </row>
+    <row r="57" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B57" s="3"/>
+      <c r="C57" s="3"/>
+    </row>
+    <row r="58" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B58" s="3"/>
+      <c r="C58" s="3"/>
+    </row>
+    <row r="59" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B59" s="3"/>
+      <c r="C59" s="3"/>
+    </row>
+    <row r="60" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B60" s="3"/>
+      <c r="C60" s="3"/>
+    </row>
+    <row r="61" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B61" s="3"/>
+      <c r="C61" s="3"/>
+    </row>
+    <row r="62" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B62" s="3"/>
+      <c r="C62" s="3"/>
+    </row>
+    <row r="63" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B63" s="3"/>
+      <c r="C63" s="3"/>
+    </row>
+    <row r="64" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B64" s="3"/>
+      <c r="C64" s="3"/>
+    </row>
+    <row r="65" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B65" s="3"/>
+      <c r="C65" s="3"/>
+    </row>
+    <row r="66" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B66" s="3"/>
+      <c r="C66" s="3"/>
+    </row>
+    <row r="67" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
+    </row>
+    <row r="68" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B68" s="3"/>
+      <c r="C68" s="3"/>
+    </row>
+    <row r="69" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B69" s="3"/>
+      <c r="C69" s="3"/>
+    </row>
+    <row r="70" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B70" s="3"/>
+      <c r="C70" s="3"/>
+    </row>
+    <row r="71" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B71" s="3"/>
+      <c r="C71" s="3"/>
+    </row>
+    <row r="72" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B72" s="3"/>
+      <c r="C72" s="3"/>
+    </row>
+    <row r="73" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B73" s="3"/>
+      <c r="C73" s="3"/>
+    </row>
+    <row r="74" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B74" s="3"/>
+      <c r="C74" s="3"/>
+    </row>
+    <row r="75" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B75" s="3"/>
+      <c r="C75" s="3"/>
+    </row>
+    <row r="76" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B76" s="3"/>
+      <c r="C76" s="3"/>
+    </row>
+    <row r="78" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B78" s="3"/>
-      <c r="D78" s="3"/>
-      <c r="E78" s="3"/>
-      <c r="G78" s="3"/>
-      <c r="H78" s="3"/>
-      <c r="I78" s="3"/>
-      <c r="M78" s="3"/>
-      <c r="N78"/>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="H79" s="3"/>
-      <c r="I79" s="3"/>
-      <c r="N79"/>
-    </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="H80" s="3"/>
-      <c r="I80" s="3"/>
-      <c r="N80"/>
-    </row>
-    <row r="81" spans="8:14" x14ac:dyDescent="0.25">
-      <c r="H81" s="3"/>
-      <c r="I81" s="3"/>
-      <c r="N81"/>
-    </row>
-    <row r="82" spans="8:14" x14ac:dyDescent="0.25">
-      <c r="H82" s="3"/>
-      <c r="I82" s="3"/>
-      <c r="N82"/>
+      <c r="C78" s="3"/>
+    </row>
+    <row r="79" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B79" s="3"/>
+      <c r="C79" s="3"/>
+    </row>
+    <row r="80" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B80" s="3"/>
+      <c r="C80" s="3"/>
+    </row>
+    <row r="81" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B81" s="3"/>
+      <c r="C81" s="3"/>
+    </row>
+    <row r="82" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B82" s="3"/>
+      <c r="C82" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:P5" xr:uid="{B692AEE8-68EE-4B81-A49D-50BF066DFFE7}"/>
+  <autoFilter ref="A3:H5" xr:uid="{B692AEE8-68EE-4B81-A49D-50BF066DFFE7}"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3055,13 +2819,13 @@
         <v>5</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>5</v>
@@ -3085,34 +2849,34 @@
       <c r="J2" s="2"/>
     </row>
     <row r="3" spans="1:10" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
-        <v>176</v>
-      </c>
-      <c r="B3" s="9" t="s">
+      <c r="A3" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="F3" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="I3" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="J3" s="9" t="s">
+      <c r="F3" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="J3" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3192,57 +2956,57 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>210</v>
-      </c>
-      <c r="B1" s="25" t="s">
+        <v>203</v>
+      </c>
+      <c r="B1" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="D1" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="E1" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="F1" s="25" t="s">
-        <v>155</v>
-      </c>
-      <c r="G1" s="25" t="s">
+      <c r="F1" s="22" t="s">
+        <v>149</v>
+      </c>
+      <c r="G1" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="H1" s="25" t="s">
+      <c r="H1" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="I1" s="25" t="s">
+      <c r="I1" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="J1" s="25" t="s">
+      <c r="J1" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="K1" s="25" t="s">
-        <v>169</v>
-      </c>
-      <c r="L1" s="25" t="s">
+      <c r="K1" s="22" t="s">
+        <v>163</v>
+      </c>
+      <c r="L1" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="M1" s="25" t="s">
+      <c r="M1" s="22" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="B2" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -3259,22 +3023,22 @@
       <c r="J2" t="s">
         <v>99</v>
       </c>
-      <c r="K2" s="24" t="b">
+      <c r="K2" s="21" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -3291,25 +3055,25 @@
       <c r="J3" t="s">
         <v>99</v>
       </c>
-      <c r="K3" s="24" t="b">
+      <c r="K3" s="21" t="b">
         <v>1</v>
       </c>
       <c r="L3" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="B4" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -3326,22 +3090,22 @@
       <c r="J4" t="s">
         <v>99</v>
       </c>
-      <c r="K4" s="24" t="b">
+      <c r="K4" s="21" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="B5" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -3358,25 +3122,25 @@
       <c r="J5" t="s">
         <v>99</v>
       </c>
-      <c r="K5" s="24" t="b">
+      <c r="K5" s="21" t="b">
         <v>1</v>
       </c>
       <c r="L5" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="B6" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="F6">
         <v>-100</v>
@@ -3393,7 +3157,7 @@
       <c r="J6" t="s">
         <v>99</v>
       </c>
-      <c r="K6" s="24" t="b">
+      <c r="K6" s="21" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3549,26 +3313,26 @@
       </c>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="F5" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="G5" s="18" t="s">
-        <v>162</v>
-      </c>
-      <c r="H5" s="18" t="s">
-        <v>181</v>
+      <c r="G5" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="H5" s="15" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.25">
@@ -3588,10 +3352,10 @@
         <v>98</v>
       </c>
       <c r="G6" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="H6" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.25">
@@ -3611,10 +3375,10 @@
         <v>99</v>
       </c>
       <c r="G7" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="H7" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.25">
@@ -3628,7 +3392,7 @@
         <v>100</v>
       </c>
       <c r="H8" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.25">
@@ -3654,12 +3418,12 @@
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -3932,15 +3696,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="7536dd80-7d39-48e8-9ae3-b4166f580a2d">
@@ -3950,6 +3705,15 @@
     <Comment xmlns="7536dd80-7d39-48e8-9ae3-b4166f580a2d" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3972,14 +3736,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8AB3C6F0-DB35-46F0-8FEB-B5E57B48A727}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{557FAA9C-B184-448F-B58D-00E4D46BDD72}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -3994,4 +3750,12 @@
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8AB3C6F0-DB35-46F0-8FEB-B5E57B48A727}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>